--- a/Projeto/Docs/Scripts.xlsx
+++ b/Projeto/Docs/Scripts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fields Online\Projeto\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8842662D-D900-4B5B-A411-B314388856D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B65B9FB-52A0-4D64-AD9F-CA6A5711C785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27075" yWindow="1905" windowWidth="9810" windowHeight="11550" xr2:uid="{3617122B-C517-4F26-98F5-D768E9F29D51}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>====Fields Online=======</t>
   </si>
@@ -114,6 +114,21 @@
   </si>
   <si>
     <t>FO_EntityVisualSystem</t>
+  </si>
+  <si>
+    <t>[FO] Runtime</t>
+  </si>
+  <si>
+    <t>FO_EntityRuntimeSystem</t>
+  </si>
+  <si>
+    <t>FO_FloatingDamageSystem</t>
+  </si>
+  <si>
+    <t>FO_AutoAttackSystem</t>
+  </si>
+  <si>
+    <t>FO_TargetVisualSystem</t>
   </si>
 </sst>
 </file>
@@ -485,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD1BA11-D9B9-470C-9224-DD97D63CE114}">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -588,35 +603,61 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Projeto/Docs/Scripts.xlsx
+++ b/Projeto/Docs/Scripts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fields Online\Projeto\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B65B9FB-52A0-4D64-AD9F-CA6A5711C785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F7C359-B0D0-4AA9-AA10-B9EF9C156893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27075" yWindow="1905" windowWidth="9810" windowHeight="11550" xr2:uid="{3617122B-C517-4F26-98F5-D768E9F29D51}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>====Fields Online=======</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>FO_TargetVisualSystem</t>
+  </si>
+  <si>
+    <t>FO_MobAISystem</t>
   </si>
 </sst>
 </file>
@@ -500,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD1BA11-D9B9-470C-9224-DD97D63CE114}">
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -606,53 +609,58 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>26</v>
       </c>
     </row>

--- a/Projeto/Docs/Scripts.xlsx
+++ b/Projeto/Docs/Scripts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fields Online\Projeto\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F7C359-B0D0-4AA9-AA10-B9EF9C156893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637AB3D9-E514-46CE-AA66-25D6959D88A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27075" yWindow="1905" windowWidth="9810" windowHeight="11550" xr2:uid="{3617122B-C517-4F26-98F5-D768E9F29D51}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>====Fields Online=======</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>FO_MobAISystem</t>
+  </si>
+  <si>
+    <t>FO_PlayerRuntimeSystem</t>
   </si>
 </sst>
 </file>
@@ -503,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD1BA11-D9B9-470C-9224-DD97D63CE114}">
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -664,6 +667,11 @@
         <v>26</v>
       </c>
     </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Projeto/Docs/Scripts.xlsx
+++ b/Projeto/Docs/Scripts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fields Online\Projeto\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637AB3D9-E514-46CE-AA66-25D6959D88A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E7F580-6F81-41E0-ADD1-F8376602566C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27075" yWindow="1905" windowWidth="9810" windowHeight="11550" xr2:uid="{3617122B-C517-4F26-98F5-D768E9F29D51}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{3617122B-C517-4F26-98F5-D768E9F29D51}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>====Fields Online=======</t>
   </si>
@@ -135,6 +135,30 @@
   </si>
   <si>
     <t>FO_PlayerRuntimeSystem</t>
+  </si>
+  <si>
+    <t>[FO] HUD</t>
+  </si>
+  <si>
+    <t>FO_PlayerHUDSystem</t>
+  </si>
+  <si>
+    <t>FO_InteractionSystem</t>
+  </si>
+  <si>
+    <t>FO_PlayerLevelSystem</t>
+  </si>
+  <si>
+    <t>FO_PlayerEXPBarSystem</t>
+  </si>
+  <si>
+    <t>FO_LootSystem</t>
+  </si>
+  <si>
+    <t>FO_FloatingLootSystem</t>
+  </si>
+  <si>
+    <t>FO_DatabaseBridge</t>
   </si>
 </sst>
 </file>
@@ -506,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD1BA11-D9B9-470C-9224-DD97D63CE114}">
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -529,7 +553,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -539,22 +563,22 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -564,112 +588,152 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>20</v>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Projeto/Docs/Scripts.xlsx
+++ b/Projeto/Docs/Scripts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fields Online\Projeto\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E7F580-6F81-41E0-ADD1-F8376602566C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1700D61C-792B-47F1-8732-2F72F3D738A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{3617122B-C517-4F26-98F5-D768E9F29D51}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>====Fields Online=======</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>FO_DatabaseBridge</t>
+  </si>
+  <si>
+    <t>FO_ConsumableSystem</t>
   </si>
 </sst>
 </file>
@@ -530,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD1BA11-D9B9-470C-9224-DD97D63CE114}">
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -628,111 +631,116 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>38</v>
       </c>
     </row>

--- a/Projeto/Docs/Scripts.xlsx
+++ b/Projeto/Docs/Scripts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fields Online\Projeto\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1700D61C-792B-47F1-8732-2F72F3D738A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF062CD3-2AE3-4300-B197-7E7E1DCCE97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{3617122B-C517-4F26-98F5-D768E9F29D51}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>====Fields Online=======</t>
   </si>
@@ -162,6 +162,12 @@
   </si>
   <si>
     <t>FO_ConsumableSystem</t>
+  </si>
+  <si>
+    <t>[FO] Tags</t>
+  </si>
+  <si>
+    <t>FO_ConsumableTags</t>
   </si>
 </sst>
 </file>
@@ -533,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD1BA11-D9B9-470C-9224-DD97D63CE114}">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -606,141 +612,151 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="29" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="30" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="31" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>38</v>
       </c>
     </row>
